--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2283" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="265">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Patient / Usager</t>
+    <t>1.1- Patient / Usager</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:26:54+00:00</t>
+    <t>2025-01-23T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -313,14 +313,21 @@
     <t>PatientDocument.personnePhysique.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -343,7 +350,21 @@
     <t>PatientDocument.personnePhysique.modifierExtension</t>
   </si>
   <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -526,80 +547,79 @@
     <t>Prénom du représentant.</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.representantPatient.structureRepresentatntPatient</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient</t>
   </si>
   <si>
     <t>Structure représentant le patient/usager.</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.representantPatient.structureRepresentatntPatient.id</t>
-  </si>
-  <si>
-    <t>PatientDocument.personnePhysique.representantPatient.structureRepresentatntPatient.extension</t>
-  </si>
-  <si>
-    <t>PatientDocument.personnePhysique.representantPatient.structureRepresentatntPatient.modifierExtension</t>
-  </si>
-  <si>
-    <t>PatientDocument.personnePhysique.representantPatient.structureRepresentatntPatient.identifiant</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.id</t>
+  </si>
+  <si>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.extension</t>
+  </si>
+  <si>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.modifierExtension</t>
+  </si>
+  <si>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.identifiant</t>
   </si>
   <si>
     <t>Identifiant de la structure.</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.representantPatient.structureRepresentatntPatient.nom</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.nom</t>
   </si>
   <si>
     <t>Nom de la structure.</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance</t>
   </si>
   <si>
     <t>Lieu de naissance.</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.id</t>
-  </si>
-  <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.extension</t>
-  </si>
-  <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.modifierExtension</t>
-  </si>
-  <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.nomLieuNaissance</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.id</t>
+  </si>
+  <si>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.extension</t>
+  </si>
+  <si>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.modifierExtension</t>
+  </si>
+  <si>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu</t>
+  </si>
+  <si>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.id</t>
+  </si>
+  <si>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.extension</t>
+  </si>
+  <si>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.modifierExtension</t>
+  </si>
+  <si>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.nomLieuNaissance</t>
   </si>
   <si>
     <t>Nom du lieu de naissance du patient/usager.</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.adresseEtCOG</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.adresseEtCodeOfficielGeographique</t>
   </si>
   <si>
     <t>Adresse et code officiel géographique du lieu de naissance.</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.adresseEtCOG.id</t>
-  </si>
-  <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.adresseEtCOG.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.adresseEtCOG.use</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.adresseEtCodeOfficielGeographique.id</t>
+  </si>
+  <si>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.adresseEtCodeOfficielGeographique.extension</t>
+  </si>
+  <si>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.adresseEtCodeOfficielGeographique.use</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -633,7 +653,7 @@
     <t>Address.use</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.adresseEtCOG.type</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.adresseEtCodeOfficielGeographique.type</t>
   </si>
   <si>
     <t>postal | physical | both</t>
@@ -657,7 +677,7 @@
     <t>Address.type</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.adresseEtCOG.text</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.adresseEtCodeOfficielGeographique.text</t>
   </si>
   <si>
     <t>Text representation of the address</t>
@@ -678,7 +698,7 @@
     <t>Address.text</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.adresseEtCOG.line</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.adresseEtCodeOfficielGeographique.line</t>
   </si>
   <si>
     <t>Street name, number, direction &amp; P.O. Box etc.</t>
@@ -693,7 +713,7 @@
     <t>Address.line</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.adresseEtCOG.city</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.adresseEtCodeOfficielGeographique.city</t>
   </si>
   <si>
     <t xml:space="preserve">Municpality
@@ -712,7 +732,7 @@
     <t>Address.city</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.adresseEtCOG.district</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.adresseEtCodeOfficielGeographique.district</t>
   </si>
   <si>
     <t xml:space="preserve">County
@@ -734,7 +754,7 @@
     <t>Address.district</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.adresseEtCOG.state</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.adresseEtCodeOfficielGeographique.state</t>
   </si>
   <si>
     <t>Province
@@ -750,7 +770,7 @@
     <t>Address.state</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.adresseEtCOG.postalCode</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.adresseEtCodeOfficielGeographique.postalCode</t>
   </si>
   <si>
     <t xml:space="preserve">Zip
@@ -769,7 +789,7 @@
     <t>Address.postalCode</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.adresseEtCOG.country</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.adresseEtCodeOfficielGeographique.country</t>
   </si>
   <si>
     <t>Country (e.g. can be ISO 3166 2 or 3 letter code)</t>
@@ -784,7 +804,7 @@
     <t>Address.country</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.adresseEtCOG.period</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.adresseEtCodeOfficielGeographique.period</t>
   </si>
   <si>
     <t xml:space="preserve">Period
@@ -809,7 +829,7 @@
     <t>Address.period</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.lieuNaissance.adresseEtCOG.COG</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.structureRepresentatntPatient.lieuNaissance.lieu.adresseEtCodeOfficielGeographique.CodeOfficielGeographique</t>
   </si>
   <si>
     <t>Code Officiel Géographique (COG) de la commune ou du pays du lieu de naissance.</t>
@@ -1114,13 +1134,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ72"/>
+  <dimension ref="A1:AJ76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="110.328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="110.328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="185.51171875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="185.51171875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="21.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
@@ -1131,7 +1151,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="59.8515625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -1148,7 +1168,7 @@
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="100.82421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="185.51171875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1780,7 +1800,7 @@
         <v>73</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>72</v>
@@ -1873,14 +1893,14 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>72</v>
@@ -1892,15 +1912,17 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N8" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>72</v>
@@ -1937,19 +1959,19 @@
         <v>72</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AD8" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>73</v>
@@ -1961,47 +1983,51 @@
         <v>72</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="O9" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="P9" t="s" s="2">
         <v>72</v>
       </c>
@@ -2049,7 +2075,7 @@
         <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
@@ -2061,15 +2087,15 @@
         <v>72</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2095,10 +2121,10 @@
         <v>88</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2149,7 +2175,7 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
@@ -2166,10 +2192,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2180,7 +2206,7 @@
         <v>73</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>72</v>
@@ -2266,21 +2292,21 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>72</v>
@@ -2292,15 +2318,17 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>72</v>
@@ -2337,19 +2365,19 @@
         <v>72</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -2361,47 +2389,51 @@
         <v>72</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>72</v>
       </c>
@@ -2449,7 +2481,7 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
@@ -2461,15 +2493,15 @@
         <v>72</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2495,10 +2527,10 @@
         <v>88</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2549,7 +2581,7 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
@@ -2566,10 +2598,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2580,7 +2612,7 @@
         <v>73</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>72</v>
@@ -2666,21 +2698,21 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>72</v>
@@ -2692,15 +2724,17 @@
         <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>72</v>
@@ -2737,19 +2771,19 @@
         <v>72</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>73</v>
@@ -2761,47 +2795,51 @@
         <v>72</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>72</v>
       </c>
@@ -2849,7 +2887,7 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>73</v>
@@ -2861,15 +2899,15 @@
         <v>72</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2895,10 +2933,10 @@
         <v>92</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2949,7 +2987,7 @@
         <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>73</v>
@@ -2966,10 +3004,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2995,10 +3033,10 @@
         <v>92</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3049,7 +3087,7 @@
         <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
@@ -3066,10 +3104,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3095,10 +3133,10 @@
         <v>88</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3149,7 +3187,7 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
@@ -3166,10 +3204,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3180,7 +3218,7 @@
         <v>73</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>72</v>
@@ -3266,21 +3304,21 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>72</v>
@@ -3292,15 +3330,17 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>72</v>
@@ -3337,19 +3377,19 @@
         <v>72</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
@@ -3361,47 +3401,51 @@
         <v>72</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>72</v>
       </c>
@@ -3449,7 +3493,7 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -3461,15 +3505,15 @@
         <v>72</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3495,10 +3539,10 @@
         <v>92</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3549,7 +3593,7 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -3566,10 +3610,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3595,10 +3639,10 @@
         <v>92</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3649,7 +3693,7 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
@@ -3666,10 +3710,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3695,10 +3739,10 @@
         <v>92</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3749,7 +3793,7 @@
         <v>72</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>
@@ -3766,10 +3810,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3792,13 +3836,13 @@
         <v>72</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3849,7 +3893,7 @@
         <v>72</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -3866,10 +3910,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3892,13 +3936,13 @@
         <v>72</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3949,7 +3993,7 @@
         <v>72</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -3966,10 +4010,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3992,13 +4036,13 @@
         <v>72</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4049,7 +4093,7 @@
         <v>72</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>73</v>
@@ -4066,10 +4110,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4092,13 +4136,13 @@
         <v>72</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4149,7 +4193,7 @@
         <v>72</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>73</v>
@@ -4166,10 +4210,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4195,10 +4239,10 @@
         <v>92</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4249,7 +4293,7 @@
         <v>72</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>73</v>
@@ -4266,10 +4310,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4295,10 +4339,10 @@
         <v>88</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4349,7 +4393,7 @@
         <v>72</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>73</v>
@@ -4366,10 +4410,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4380,7 +4424,7 @@
         <v>73</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>72</v>
@@ -4466,21 +4510,21 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>72</v>
@@ -4492,15 +4536,17 @@
         <v>72</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>72</v>
@@ -4537,19 +4583,19 @@
         <v>72</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>73</v>
@@ -4561,47 +4607,51 @@
         <v>72</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>72</v>
       </c>
@@ -4649,7 +4699,7 @@
         <v>72</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>73</v>
@@ -4661,15 +4711,15 @@
         <v>72</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4695,10 +4745,10 @@
         <v>82</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4749,7 +4799,7 @@
         <v>72</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>73</v>
@@ -4766,10 +4816,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4795,10 +4845,10 @@
         <v>85</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4849,7 +4899,7 @@
         <v>72</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>73</v>
@@ -4866,10 +4916,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4895,10 +4945,10 @@
         <v>88</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4949,7 +4999,7 @@
         <v>72</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>73</v>
@@ -4966,10 +5016,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4980,7 +5030,7 @@
         <v>73</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>72</v>
@@ -5066,21 +5116,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>72</v>
@@ -5092,15 +5142,17 @@
         <v>72</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>72</v>
@@ -5137,19 +5189,19 @@
         <v>72</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>73</v>
@@ -5161,47 +5213,51 @@
         <v>72</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>72</v>
       </c>
@@ -5249,7 +5305,7 @@
         <v>72</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>73</v>
@@ -5261,15 +5317,15 @@
         <v>72</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5295,10 +5351,10 @@
         <v>88</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5349,7 +5405,7 @@
         <v>72</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>73</v>
@@ -5366,10 +5422,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5380,7 +5436,7 @@
         <v>73</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>72</v>
@@ -5466,21 +5522,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>72</v>
@@ -5492,15 +5548,17 @@
         <v>72</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>72</v>
@@ -5537,19 +5595,19 @@
         <v>72</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>73</v>
@@ -5561,47 +5619,51 @@
         <v>72</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>72</v>
       </c>
@@ -5649,7 +5711,7 @@
         <v>72</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>73</v>
@@ -5661,15 +5723,15 @@
         <v>72</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5695,10 +5757,10 @@
         <v>92</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5749,7 +5811,7 @@
         <v>72</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>73</v>
@@ -5766,10 +5828,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5795,10 +5857,10 @@
         <v>92</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5849,7 +5911,7 @@
         <v>72</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>73</v>
@@ -5866,10 +5928,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5895,10 +5957,10 @@
         <v>88</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -5949,7 +6011,7 @@
         <v>72</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>73</v>
@@ -5966,10 +6028,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -5980,7 +6042,7 @@
         <v>73</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>72</v>
@@ -6066,21 +6128,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>72</v>
@@ -6092,15 +6154,17 @@
         <v>72</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>72</v>
@@ -6137,19 +6201,19 @@
         <v>72</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>73</v>
@@ -6161,47 +6225,51 @@
         <v>72</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>72</v>
       </c>
@@ -6249,7 +6317,7 @@
         <v>72</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>73</v>
@@ -6261,15 +6329,15 @@
         <v>72</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6295,10 +6363,10 @@
         <v>79</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6349,7 +6417,7 @@
         <v>72</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>73</v>
@@ -6366,10 +6434,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6395,10 +6463,10 @@
         <v>92</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6449,7 +6517,7 @@
         <v>72</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>73</v>
@@ -6466,10 +6534,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6495,10 +6563,10 @@
         <v>88</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6549,7 +6617,7 @@
         <v>72</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>73</v>
@@ -6566,10 +6634,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6580,7 +6648,7 @@
         <v>73</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>72</v>
@@ -6666,21 +6734,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>72</v>
@@ -6692,15 +6760,17 @@
         <v>72</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>72</v>
@@ -6737,19 +6807,19 @@
         <v>72</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>73</v>
@@ -6761,47 +6831,51 @@
         <v>72</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>72</v>
       </c>
@@ -6849,7 +6923,7 @@
         <v>72</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>73</v>
@@ -6861,15 +6935,15 @@
         <v>72</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -6877,7 +6951,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>78</v>
@@ -6892,13 +6966,13 @@
         <v>72</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -6949,10 +7023,10 @@
         <v>72</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>78</v>
@@ -6961,15 +7035,15 @@
         <v>72</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -6992,13 +7066,13 @@
         <v>72</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>183</v>
+        <v>93</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>183</v>
+        <v>94</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7049,7 +7123,7 @@
         <v>72</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>73</v>
@@ -7061,26 +7135,26 @@
         <v>72</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>90</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>72</v>
@@ -7092,15 +7166,17 @@
         <v>72</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>72</v>
@@ -7137,43 +7213,43 @@
         <v>72</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>72</v>
+        <v>106</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>186</v>
+        <v>108</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -7186,24 +7262,26 @@
         <v>72</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>187</v>
+        <v>110</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>188</v>
+        <v>111</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>72</v>
       </c>
@@ -7239,19 +7317,19 @@
         <v>72</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>73</v>
@@ -7263,7 +7341,7 @@
         <v>72</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="62">
@@ -7288,26 +7366,22 @@
         <v>72</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L62" t="s" s="2">
-        <v>192</v>
-      </c>
       <c r="M62" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>72</v>
       </c>
@@ -7319,7 +7393,7 @@
         <v>72</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>72</v>
@@ -7331,13 +7405,13 @@
         <v>72</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>197</v>
+        <v>72</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>199</v>
+        <v>72</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>72</v>
@@ -7355,7 +7429,7 @@
         <v>72</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>73</v>
@@ -7367,15 +7441,15 @@
         <v>72</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>90</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7395,20 +7469,18 @@
         <v>72</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>191</v>
+        <v>82</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>72</v>
@@ -7421,7 +7493,7 @@
         <v>72</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>205</v>
+        <v>72</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>72</v>
@@ -7433,13 +7505,13 @@
         <v>72</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>197</v>
+        <v>72</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>206</v>
+        <v>72</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>207</v>
+        <v>72</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>72</v>
@@ -7457,7 +7529,7 @@
         <v>72</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>73</v>
@@ -7474,10 +7546,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7497,23 +7569,19 @@
         <v>72</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>92</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>72</v>
       </c>
@@ -7525,7 +7593,7 @@
         <v>72</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>214</v>
+        <v>72</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>72</v>
@@ -7561,7 +7629,7 @@
         <v>72</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>215</v>
+        <v>95</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>73</v>
@@ -7573,19 +7641,19 @@
         <v>72</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>90</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -7601,18 +7669,20 @@
         <v>72</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>217</v>
+        <v>99</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>72</v>
@@ -7625,7 +7695,7 @@
         <v>72</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>219</v>
+        <v>72</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>72</v>
@@ -7649,19 +7719,19 @@
         <v>72</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>220</v>
+        <v>105</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>73</v>
@@ -7673,19 +7743,19 @@
         <v>72</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>90</v>
+        <v>106</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>222</v>
+        <v>72</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -7698,22 +7768,26 @@
         <v>72</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>92</v>
+        <v>197</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>72</v>
       </c>
@@ -7725,7 +7799,7 @@
         <v>72</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>72</v>
@@ -7737,13 +7811,13 @@
         <v>72</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>72</v>
+        <v>203</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>72</v>
+        <v>204</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>72</v>
+        <v>205</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>72</v>
@@ -7761,7 +7835,7 @@
         <v>72</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>73</v>
@@ -7778,14 +7852,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>228</v>
+        <v>72</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -7801,19 +7875,19 @@
         <v>72</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>92</v>
+        <v>197</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -7827,7 +7901,7 @@
         <v>72</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>72</v>
@@ -7839,13 +7913,13 @@
         <v>72</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>72</v>
+        <v>203</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>72</v>
+        <v>212</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>72</v>
+        <v>213</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>72</v>
@@ -7863,7 +7937,7 @@
         <v>72</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>73</v>
@@ -7880,14 +7954,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>235</v>
+        <v>72</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -7903,19 +7977,23 @@
         <v>72</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>92</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>72</v>
       </c>
@@ -7927,7 +8005,7 @@
         <v>72</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>72</v>
+        <v>220</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>72</v>
@@ -7963,7 +8041,7 @@
         <v>72</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>73</v>
@@ -7980,21 +8058,21 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>240</v>
+        <v>72</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>72</v>
@@ -8003,16 +8081,16 @@
         <v>72</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K69" t="s" s="2">
         <v>92</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8027,7 +8105,7 @@
         <v>72</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>72</v>
@@ -8063,13 +8141,13 @@
         <v>72</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>72</v>
@@ -8080,14 +8158,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>72</v>
+        <v>228</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -8103,20 +8181,18 @@
         <v>72</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>92</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>72</v>
@@ -8129,7 +8205,7 @@
         <v>72</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>72</v>
@@ -8165,7 +8241,7 @@
         <v>72</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>73</v>
@@ -8182,14 +8258,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>72</v>
+        <v>234</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -8205,21 +8281,21 @@
         <v>72</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>251</v>
+        <v>92</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>72</v>
       </c>
@@ -8231,7 +8307,7 @@
         <v>72</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>72</v>
@@ -8267,7 +8343,7 @@
         <v>72</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>73</v>
@@ -8284,14 +8360,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>72</v>
+        <v>241</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -8307,16 +8383,16 @@
         <v>72</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>92</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8367,18 +8443,422 @@
         <v>72</v>
       </c>
       <c r="AF72" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="K75" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AG72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
+      <c r="L75" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="266">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -398,6 +398,9 @@
   </si>
   <si>
     <t>PatientDocument.personnePhysique.nomsPrenom.noms.nomNaissance</t>
+  </si>
+  <si>
+    <t>Nom de naissance (ou nom de famille) du patient/usager. Obligatoire si le matricule INS est présent.</t>
   </si>
   <si>
     <t>PatientDocument.personnePhysique.nomsPrenom.noms.nomUtilise</t>
@@ -2933,10 +2936,10 @@
         <v>92</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3004,10 +3007,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3087,7 +3090,7 @@
         <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>73</v>
@@ -3104,10 +3107,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3133,10 +3136,10 @@
         <v>88</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3187,7 +3190,7 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
@@ -3204,10 +3207,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3304,10 +3307,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3406,10 +3409,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3510,10 +3513,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3539,10 +3542,10 @@
         <v>92</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3593,7 +3596,7 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -3610,10 +3613,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3639,10 +3642,10 @@
         <v>92</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3693,7 +3696,7 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
@@ -3710,10 +3713,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3739,10 +3742,10 @@
         <v>92</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3793,7 +3796,7 @@
         <v>72</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>
@@ -3810,10 +3813,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3836,13 +3839,13 @@
         <v>72</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3893,7 +3896,7 @@
         <v>72</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -3910,10 +3913,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3936,13 +3939,13 @@
         <v>72</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3993,7 +3996,7 @@
         <v>72</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4010,10 +4013,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4036,13 +4039,13 @@
         <v>72</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4093,7 +4096,7 @@
         <v>72</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>73</v>
@@ -4110,10 +4113,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4136,13 +4139,13 @@
         <v>72</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4193,7 +4196,7 @@
         <v>72</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>73</v>
@@ -4210,10 +4213,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4239,10 +4242,10 @@
         <v>92</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4293,7 +4296,7 @@
         <v>72</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>73</v>
@@ -4310,10 +4313,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4339,10 +4342,10 @@
         <v>88</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4393,7 +4396,7 @@
         <v>72</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>73</v>
@@ -4410,10 +4413,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4510,10 +4513,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4612,10 +4615,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4716,10 +4719,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4745,10 +4748,10 @@
         <v>82</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4799,7 +4802,7 @@
         <v>72</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>73</v>
@@ -4816,10 +4819,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4845,10 +4848,10 @@
         <v>85</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4899,7 +4902,7 @@
         <v>72</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>73</v>
@@ -4916,10 +4919,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4945,10 +4948,10 @@
         <v>88</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4999,7 +5002,7 @@
         <v>72</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>73</v>
@@ -5016,10 +5019,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5116,10 +5119,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5218,10 +5221,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5322,10 +5325,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5351,10 +5354,10 @@
         <v>88</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5405,7 +5408,7 @@
         <v>72</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>73</v>
@@ -5422,10 +5425,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5522,10 +5525,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5624,10 +5627,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5728,10 +5731,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5757,10 +5760,10 @@
         <v>92</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5811,7 +5814,7 @@
         <v>72</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>73</v>
@@ -5828,10 +5831,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5857,10 +5860,10 @@
         <v>92</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5911,7 +5914,7 @@
         <v>72</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>73</v>
@@ -5928,10 +5931,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5957,10 +5960,10 @@
         <v>88</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6011,7 +6014,7 @@
         <v>72</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>73</v>
@@ -6028,10 +6031,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6128,10 +6131,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6230,10 +6233,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6334,10 +6337,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6363,10 +6366,10 @@
         <v>79</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6417,7 +6420,7 @@
         <v>72</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>73</v>
@@ -6434,10 +6437,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6463,10 +6466,10 @@
         <v>92</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6517,7 +6520,7 @@
         <v>72</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>73</v>
@@ -6534,10 +6537,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6563,10 +6566,10 @@
         <v>88</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6617,7 +6620,7 @@
         <v>72</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>73</v>
@@ -6634,10 +6637,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6734,10 +6737,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6836,10 +6839,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6940,10 +6943,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -6969,10 +6972,10 @@
         <v>88</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7023,7 +7026,7 @@
         <v>72</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -7040,10 +7043,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7140,10 +7143,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7242,10 +7245,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7346,10 +7349,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7375,10 +7378,10 @@
         <v>92</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7429,7 +7432,7 @@
         <v>72</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>73</v>
@@ -7446,10 +7449,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7475,10 +7478,10 @@
         <v>82</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7529,7 +7532,7 @@
         <v>72</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>73</v>
@@ -7546,10 +7549,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7646,10 +7649,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7748,10 +7751,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7774,19 +7777,19 @@
         <v>109</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>72</v>
@@ -7799,7 +7802,7 @@
         <v>72</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>72</v>
@@ -7811,13 +7814,13 @@
         <v>72</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>72</v>
@@ -7835,7 +7838,7 @@
         <v>72</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>73</v>
@@ -7852,10 +7855,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -7878,16 +7881,16 @@
         <v>109</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -7901,7 +7904,7 @@
         <v>72</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>72</v>
@@ -7913,13 +7916,13 @@
         <v>72</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>72</v>
@@ -7937,7 +7940,7 @@
         <v>72</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>73</v>
@@ -7954,10 +7957,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -7983,16 +7986,16 @@
         <v>92</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>72</v>
@@ -8005,7 +8008,7 @@
         <v>72</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>72</v>
@@ -8041,7 +8044,7 @@
         <v>72</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>73</v>
@@ -8058,10 +8061,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8087,10 +8090,10 @@
         <v>92</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8105,7 +8108,7 @@
         <v>72</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>72</v>
@@ -8141,7 +8144,7 @@
         <v>72</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>73</v>
@@ -8158,14 +8161,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -8187,10 +8190,10 @@
         <v>92</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8205,7 +8208,7 @@
         <v>72</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>72</v>
@@ -8241,7 +8244,7 @@
         <v>72</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>73</v>
@@ -8258,14 +8261,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -8287,13 +8290,13 @@
         <v>92</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -8307,7 +8310,7 @@
         <v>72</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>72</v>
@@ -8343,7 +8346,7 @@
         <v>72</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>73</v>
@@ -8360,14 +8363,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -8389,10 +8392,10 @@
         <v>92</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8443,7 +8446,7 @@
         <v>72</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>73</v>
@@ -8460,14 +8463,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -8489,10 +8492,10 @@
         <v>92</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8507,7 +8510,7 @@
         <v>72</v>
       </c>
       <c r="T73" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="U73" t="s" s="2">
         <v>72</v>
@@ -8543,7 +8546,7 @@
         <v>72</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>73</v>
@@ -8560,10 +8563,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8589,13 +8592,13 @@
         <v>92</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -8645,7 +8648,7 @@
         <v>72</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>73</v>
@@ -8662,10 +8665,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8688,17 +8691,17 @@
         <v>109</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>72</v>
@@ -8711,7 +8714,7 @@
         <v>72</v>
       </c>
       <c r="T75" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="U75" t="s" s="2">
         <v>72</v>
@@ -8747,7 +8750,7 @@
         <v>72</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>73</v>
@@ -8764,10 +8767,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -8793,10 +8796,10 @@
         <v>92</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -8847,7 +8850,7 @@
         <v>72</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>73</v>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5845,7 +5845,7 @@
         <v>73</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>72</v>
@@ -5920,7 +5920,7 @@
         <v>73</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>72</v>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="267">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -404,6 +404,9 @@
   </si>
   <si>
     <t>PatientDocument.personnePhysique.nomsPrenom.noms.nomUtilise</t>
+  </si>
+  <si>
+    <t>Nom utilisé du patient/usager.</t>
   </si>
   <si>
     <t>PatientDocument.personnePhysique.nomsPrenom.prenom</t>
@@ -3036,10 +3039,10 @@
         <v>92</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3107,10 +3110,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3136,10 +3139,10 @@
         <v>88</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3190,7 +3193,7 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>73</v>
@@ -3207,10 +3210,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3307,10 +3310,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3409,10 +3412,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3513,10 +3516,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3542,10 +3545,10 @@
         <v>92</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3596,7 +3599,7 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -3613,10 +3616,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3642,10 +3645,10 @@
         <v>92</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3696,7 +3699,7 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
@@ -3713,10 +3716,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3742,10 +3745,10 @@
         <v>92</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3796,7 +3799,7 @@
         <v>72</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>
@@ -3813,10 +3816,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3839,13 +3842,13 @@
         <v>72</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3896,7 +3899,7 @@
         <v>72</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -3913,10 +3916,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3939,13 +3942,13 @@
         <v>72</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3996,7 +3999,7 @@
         <v>72</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4013,10 +4016,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4039,13 +4042,13 @@
         <v>72</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4096,7 +4099,7 @@
         <v>72</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>73</v>
@@ -4113,10 +4116,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4139,13 +4142,13 @@
         <v>72</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4196,7 +4199,7 @@
         <v>72</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>73</v>
@@ -4213,10 +4216,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4242,10 +4245,10 @@
         <v>92</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4296,7 +4299,7 @@
         <v>72</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>73</v>
@@ -4313,10 +4316,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4342,10 +4345,10 @@
         <v>88</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4396,7 +4399,7 @@
         <v>72</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>73</v>
@@ -4413,10 +4416,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4513,10 +4516,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4615,10 +4618,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4719,10 +4722,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4748,10 +4751,10 @@
         <v>82</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4802,7 +4805,7 @@
         <v>72</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>73</v>
@@ -4819,10 +4822,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4848,10 +4851,10 @@
         <v>85</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4902,7 +4905,7 @@
         <v>72</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>73</v>
@@ -4919,10 +4922,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4948,10 +4951,10 @@
         <v>88</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5002,7 +5005,7 @@
         <v>72</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>73</v>
@@ -5019,10 +5022,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5119,10 +5122,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5221,10 +5224,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5325,10 +5328,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5354,10 +5357,10 @@
         <v>88</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5408,7 +5411,7 @@
         <v>72</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>73</v>
@@ -5425,10 +5428,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5525,10 +5528,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5627,10 +5630,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5731,10 +5734,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5760,10 +5763,10 @@
         <v>92</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5814,7 +5817,7 @@
         <v>72</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>73</v>
@@ -5831,10 +5834,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5860,10 +5863,10 @@
         <v>92</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5914,7 +5917,7 @@
         <v>72</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>73</v>
@@ -5931,10 +5934,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5960,10 +5963,10 @@
         <v>88</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6014,7 +6017,7 @@
         <v>72</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>73</v>
@@ -6031,10 +6034,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6131,10 +6134,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6233,10 +6236,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6337,10 +6340,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6366,10 +6369,10 @@
         <v>79</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6420,7 +6423,7 @@
         <v>72</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>73</v>
@@ -6437,10 +6440,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6466,10 +6469,10 @@
         <v>92</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6520,7 +6523,7 @@
         <v>72</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>73</v>
@@ -6537,10 +6540,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6566,10 +6569,10 @@
         <v>88</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6620,7 +6623,7 @@
         <v>72</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>73</v>
@@ -6637,10 +6640,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6737,10 +6740,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6839,10 +6842,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6943,10 +6946,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -6972,10 +6975,10 @@
         <v>88</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7026,7 +7029,7 @@
         <v>72</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -7043,10 +7046,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7143,10 +7146,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7245,10 +7248,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7349,10 +7352,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7378,10 +7381,10 @@
         <v>92</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7432,7 +7435,7 @@
         <v>72</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>73</v>
@@ -7449,10 +7452,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7478,10 +7481,10 @@
         <v>82</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7532,7 +7535,7 @@
         <v>72</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>73</v>
@@ -7549,10 +7552,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7649,10 +7652,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7751,10 +7754,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7777,19 +7780,19 @@
         <v>109</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>72</v>
@@ -7802,7 +7805,7 @@
         <v>72</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>72</v>
@@ -7814,13 +7817,13 @@
         <v>72</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>72</v>
@@ -7838,7 +7841,7 @@
         <v>72</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>73</v>
@@ -7855,10 +7858,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -7881,16 +7884,16 @@
         <v>109</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -7904,7 +7907,7 @@
         <v>72</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>72</v>
@@ -7916,13 +7919,13 @@
         <v>72</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>72</v>
@@ -7940,7 +7943,7 @@
         <v>72</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>73</v>
@@ -7957,10 +7960,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -7986,16 +7989,16 @@
         <v>92</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>72</v>
@@ -8008,7 +8011,7 @@
         <v>72</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>72</v>
@@ -8044,7 +8047,7 @@
         <v>72</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>73</v>
@@ -8061,10 +8064,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8090,10 +8093,10 @@
         <v>92</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8108,7 +8111,7 @@
         <v>72</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>72</v>
@@ -8144,7 +8147,7 @@
         <v>72</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>73</v>
@@ -8161,14 +8164,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -8190,10 +8193,10 @@
         <v>92</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8208,7 +8211,7 @@
         <v>72</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>72</v>
@@ -8244,7 +8247,7 @@
         <v>72</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>73</v>
@@ -8261,14 +8264,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -8290,13 +8293,13 @@
         <v>92</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -8310,7 +8313,7 @@
         <v>72</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>72</v>
@@ -8346,7 +8349,7 @@
         <v>72</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>73</v>
@@ -8363,14 +8366,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -8392,10 +8395,10 @@
         <v>92</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8446,7 +8449,7 @@
         <v>72</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>73</v>
@@ -8463,14 +8466,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -8492,10 +8495,10 @@
         <v>92</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8510,7 +8513,7 @@
         <v>72</v>
       </c>
       <c r="T73" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="U73" t="s" s="2">
         <v>72</v>
@@ -8546,7 +8549,7 @@
         <v>72</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>73</v>
@@ -8563,10 +8566,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8592,13 +8595,13 @@
         <v>92</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -8648,7 +8651,7 @@
         <v>72</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>73</v>
@@ -8665,10 +8668,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8691,17 +8694,17 @@
         <v>109</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>72</v>
@@ -8714,7 +8717,7 @@
         <v>72</v>
       </c>
       <c r="T75" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="U75" t="s" s="2">
         <v>72</v>
@@ -8750,7 +8753,7 @@
         <v>72</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>73</v>
@@ -8767,10 +8770,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -8796,10 +8799,10 @@
         <v>92</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -8850,7 +8853,7 @@
         <v>72</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>73</v>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -449,7 +449,7 @@
 </t>
   </si>
   <si>
-    <t>Sexe du patient.</t>
+    <t>Sexe administratif du patient/usager.</t>
   </si>
   <si>
     <t>PatientDocument.personnePhysique.dateNaissance</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -459,7 +459,7 @@
 </t>
   </si>
   <si>
-    <t>Date de naissance.</t>
+    <t>Date et heure de naissance du patient/usager.</t>
   </si>
   <si>
     <t>PatientDocument.personnePhysique.dateDeces</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -465,14 +465,14 @@
     <t>PatientDocument.personnePhysique.dateDeces</t>
   </si>
   <si>
+    <t>Date et heure du décès du patient/usager</t>
+  </si>
+  <si>
+    <t>PatientDocument.personnePhysique.grossesseMultiple</t>
+  </si>
+  <si>
     <t xml:space="preserve">boolean
 </t>
-  </si>
-  <si>
-    <t>Patient décédé ou pas ?.</t>
-  </si>
-  <si>
-    <t>PatientDocument.personnePhysique.grossesseMultiple</t>
   </si>
   <si>
     <t>Patient né d'une grossesse multiple.</t>
@@ -4042,13 +4042,13 @@
         <v>72</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>146</v>
-      </c>
       <c r="M29" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4142,7 +4142,7 @@
         <v>72</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>148</v>
@@ -4199,7 +4199,7 @@
         <v>72</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>73</v>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -475,7 +475,7 @@
 </t>
   </si>
   <si>
-    <t>Patient né d'une grossesse multiple.</t>
+    <t>Patient/usager né d'une grossesse multiple.</t>
   </si>
   <si>
     <t>PatientDocument.personnePhysique.numeroOrdreNaissance</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -526,28 +526,28 @@
     <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.modifierExtension</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.nomPrenom</t>
-  </si>
-  <si>
-    <t>Nom et Prénom du représentant.</t>
-  </si>
-  <si>
-    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.nomPrenom.id</t>
-  </si>
-  <si>
-    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.nomPrenom.extension</t>
-  </si>
-  <si>
-    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.nomPrenom.modifierExtension</t>
-  </si>
-  <si>
-    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.nomPrenom.nom</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenoms</t>
+  </si>
+  <si>
+    <t>Noms et prénoms du représentant.</t>
+  </si>
+  <si>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenoms.id</t>
+  </si>
+  <si>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenoms.extension</t>
+  </si>
+  <si>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenoms.modifierExtension</t>
+  </si>
+  <si>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenoms.nom</t>
   </si>
   <si>
     <t>Nom du représentant.</t>
   </si>
   <si>
-    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.nomPrenom.prenom</t>
+    <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenoms.prenom</t>
   </si>
   <si>
     <t>Prénom du représentant.</t>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>78</v>
@@ -5414,7 +5414,7 @@
         <v>165</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>78</v>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2437" uniqueCount="268">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -542,6 +542,9 @@
   </si>
   <si>
     <t>PatientDocument.personnePhysique.representantPatient.personneRepresentantPatient.nomsPrenoms.nom</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>Nom du représentant.</t>
@@ -5745,10 +5748,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>72</v>
@@ -5763,10 +5766,10 @@
         <v>92</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5820,10 +5823,10 @@
         <v>170</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>72</v>
@@ -5834,10 +5837,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5863,10 +5866,10 @@
         <v>92</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5917,7 +5920,7 @@
         <v>72</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>73</v>
@@ -5934,10 +5937,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5963,10 +5966,10 @@
         <v>88</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6017,7 +6020,7 @@
         <v>72</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>73</v>
@@ -6034,10 +6037,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6134,10 +6137,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6236,10 +6239,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6340,10 +6343,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6369,10 +6372,10 @@
         <v>79</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6423,7 +6426,7 @@
         <v>72</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>73</v>
@@ -6440,10 +6443,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6469,10 +6472,10 @@
         <v>92</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6523,7 +6526,7 @@
         <v>72</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>73</v>
@@ -6540,10 +6543,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6569,10 +6572,10 @@
         <v>88</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6623,7 +6626,7 @@
         <v>72</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>73</v>
@@ -6640,10 +6643,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6740,10 +6743,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6842,10 +6845,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6946,10 +6949,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -6975,10 +6978,10 @@
         <v>88</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7029,7 +7032,7 @@
         <v>72</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -7046,10 +7049,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7146,10 +7149,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7248,10 +7251,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7352,10 +7355,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7381,10 +7384,10 @@
         <v>92</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7435,7 +7438,7 @@
         <v>72</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>73</v>
@@ -7452,10 +7455,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7481,10 +7484,10 @@
         <v>82</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7535,7 +7538,7 @@
         <v>72</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>73</v>
@@ -7552,10 +7555,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7652,10 +7655,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7754,10 +7757,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7780,19 +7783,19 @@
         <v>109</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>72</v>
@@ -7805,7 +7808,7 @@
         <v>72</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>72</v>
@@ -7817,13 +7820,13 @@
         <v>72</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>72</v>
@@ -7841,7 +7844,7 @@
         <v>72</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>73</v>
@@ -7858,10 +7861,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -7884,16 +7887,16 @@
         <v>109</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -7907,7 +7910,7 @@
         <v>72</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>72</v>
@@ -7919,13 +7922,13 @@
         <v>72</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>72</v>
@@ -7943,7 +7946,7 @@
         <v>72</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>73</v>
@@ -7960,10 +7963,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -7989,16 +7992,16 @@
         <v>92</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>72</v>
@@ -8011,7 +8014,7 @@
         <v>72</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>72</v>
@@ -8047,7 +8050,7 @@
         <v>72</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>73</v>
@@ -8064,10 +8067,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8093,10 +8096,10 @@
         <v>92</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8111,7 +8114,7 @@
         <v>72</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>72</v>
@@ -8147,7 +8150,7 @@
         <v>72</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>73</v>
@@ -8164,14 +8167,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -8193,10 +8196,10 @@
         <v>92</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8211,7 +8214,7 @@
         <v>72</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>72</v>
@@ -8247,7 +8250,7 @@
         <v>72</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>73</v>
@@ -8264,14 +8267,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -8293,13 +8296,13 @@
         <v>92</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -8313,7 +8316,7 @@
         <v>72</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>72</v>
@@ -8349,7 +8352,7 @@
         <v>72</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>73</v>
@@ -8366,14 +8369,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -8395,10 +8398,10 @@
         <v>92</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8449,7 +8452,7 @@
         <v>72</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>73</v>
@@ -8466,14 +8469,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -8495,10 +8498,10 @@
         <v>92</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8513,7 +8516,7 @@
         <v>72</v>
       </c>
       <c r="T73" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="U73" t="s" s="2">
         <v>72</v>
@@ -8549,7 +8552,7 @@
         <v>72</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>73</v>
@@ -8566,10 +8569,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8595,13 +8598,13 @@
         <v>92</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -8651,7 +8654,7 @@
         <v>72</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>73</v>
@@ -8668,10 +8671,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8694,17 +8697,17 @@
         <v>109</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>72</v>
@@ -8717,7 +8720,7 @@
         <v>72</v>
       </c>
       <c r="T75" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="U75" t="s" s="2">
         <v>72</v>
@@ -8753,7 +8756,7 @@
         <v>72</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>73</v>
@@ -8770,10 +8773,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -8799,10 +8802,10 @@
         <v>92</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -8853,7 +8856,7 @@
         <v>72</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>73</v>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-PatientDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
